--- a/configs/CAN_MQTT_ID_Table.xlsx
+++ b/configs/CAN_MQTT_ID_Table.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Farou\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Farou\Desktop\Robotics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBE41B35-0298-471B-9AF4-18F3DDFBE251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63663213-2A39-482A-91D9-6AF17E1A5475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="170">
   <si>
     <t>ID Hex</t>
   </si>
@@ -175,25 +175,13 @@
     <t>0x41</t>
   </si>
   <si>
-    <t>hookload/ping</t>
-  </si>
-  <si>
     <t>0x42</t>
   </si>
   <si>
-    <t>hookload/tara</t>
-  </si>
-  <si>
     <t>0x43</t>
   </si>
   <si>
-    <t>hookload/data</t>
-  </si>
-  <si>
     <t>0x44</t>
-  </si>
-  <si>
-    <t>hookload/cali</t>
   </si>
   <si>
     <t>0x50</t>
@@ -557,13 +545,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -578,7 +568,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -586,32 +576,23 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -918,21 +899,21 @@
   <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="16.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -946,7 +927,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -960,7 +941,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -974,7 +955,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -988,7 +969,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -1002,7 +983,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
@@ -1016,7 +997,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>18</v>
       </c>
@@ -1030,7 +1011,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
@@ -1044,7 +1025,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -1058,7 +1039,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
@@ -1072,7 +1053,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>26</v>
       </c>
@@ -1086,7 +1067,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>28</v>
       </c>
@@ -1100,7 +1081,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>30</v>
       </c>
@@ -1114,7 +1095,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -1128,7 +1109,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
@@ -1142,7 +1123,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>36</v>
       </c>
@@ -1156,7 +1137,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>38</v>
       </c>
@@ -1170,7 +1151,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>40</v>
       </c>
@@ -1184,7 +1165,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>42</v>
       </c>
@@ -1198,7 +1179,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>44</v>
       </c>
@@ -1212,7 +1193,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>46</v>
       </c>
@@ -1226,7 +1207,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>48</v>
       </c>
@@ -1240,7 +1221,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>50</v>
       </c>
@@ -1250,27 +1231,27 @@
       <c r="C24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="B25" s="2">
         <v>66</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B26" s="2">
         <v>67</v>
@@ -1278,13 +1259,13 @@
       <c r="C26" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D26" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B27" s="2">
         <v>68</v>
@@ -1292,13 +1273,13 @@
       <c r="C27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D27" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="B28" s="2">
         <v>80</v>
@@ -1307,12 +1288,12 @@
         <v>5</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="B29" s="2">
         <v>81</v>
@@ -1321,12 +1302,12 @@
         <v>12</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="B30" s="2">
         <v>83</v>
@@ -1335,12 +1316,12 @@
         <v>5</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="B31" s="2">
         <v>84</v>
@@ -1349,12 +1330,12 @@
         <v>12</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B32" s="2">
         <v>85</v>
@@ -1363,12 +1344,12 @@
         <v>12</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B33" s="2">
         <v>96</v>
@@ -1377,12 +1358,12 @@
         <v>5</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="B34" s="2">
         <v>97</v>
@@ -1391,12 +1372,12 @@
         <v>12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B35" s="2">
         <v>98</v>
@@ -1405,12 +1386,12 @@
         <v>12</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B36" s="2">
         <v>99</v>
@@ -1419,12 +1400,12 @@
         <v>5</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B37" s="2">
         <v>100</v>
@@ -1433,12 +1414,12 @@
         <v>12</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="B38" s="2">
         <v>112</v>
@@ -1447,12 +1428,12 @@
         <v>5</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B39" s="2">
         <v>113</v>
@@ -1461,12 +1442,12 @@
         <v>12</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B40" s="2">
         <v>115</v>
@@ -1475,12 +1456,12 @@
         <v>5</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B41" s="2">
         <v>116</v>
@@ -1489,12 +1470,12 @@
         <v>12</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B42" s="2">
         <v>117</v>
@@ -1503,12 +1484,12 @@
         <v>12</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B43" s="2">
         <v>118</v>
@@ -1517,12 +1498,12 @@
         <v>12</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B44" s="2">
         <v>121</v>
@@ -1531,12 +1512,12 @@
         <v>12</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B45" s="2">
         <v>128</v>
@@ -1545,12 +1526,12 @@
         <v>5</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B46" s="2">
         <v>129</v>
@@ -1559,12 +1540,12 @@
         <v>12</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B47" s="2">
         <v>131</v>
@@ -1573,12 +1554,12 @@
         <v>5</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B48" s="2">
         <v>132</v>
@@ -1587,12 +1568,12 @@
         <v>12</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="B49" s="2">
         <v>133</v>
@@ -1601,12 +1582,12 @@
         <v>12</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B50" s="2">
         <v>134</v>
@@ -1615,12 +1596,12 @@
         <v>12</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B51" s="2">
         <v>144</v>
@@ -1629,12 +1610,12 @@
         <v>5</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B52" s="2">
         <v>145</v>
@@ -1643,12 +1624,12 @@
         <v>12</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B53" s="2">
         <v>146</v>
@@ -1657,12 +1638,12 @@
         <v>12</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B54" s="2">
         <v>147</v>
@@ -1671,12 +1652,12 @@
         <v>5</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B55" s="2">
         <v>160</v>
@@ -1685,12 +1666,12 @@
         <v>5</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B56" s="2">
         <v>161</v>
@@ -1699,12 +1680,12 @@
         <v>12</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="B57" s="2">
         <v>163</v>
@@ -1713,12 +1694,12 @@
         <v>5</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B58" s="2">
         <v>164</v>
@@ -1727,12 +1708,12 @@
         <v>12</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B59" s="2">
         <v>166</v>
@@ -1741,12 +1722,12 @@
         <v>12</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B60" s="2">
         <v>176</v>
@@ -1755,12 +1736,12 @@
         <v>5</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B61" s="2">
         <v>177</v>
@@ -1769,12 +1750,12 @@
         <v>12</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B62" s="2">
         <v>178</v>
@@ -1783,12 +1764,12 @@
         <v>12</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B63" s="2">
         <v>180</v>
@@ -1797,12 +1778,12 @@
         <v>12</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B64" s="2">
         <v>192</v>
@@ -1811,12 +1792,12 @@
         <v>5</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="B65" s="2">
         <v>193</v>
@@ -1825,12 +1806,12 @@
         <v>12</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B66" s="2">
         <v>195</v>
@@ -1839,12 +1820,12 @@
         <v>5</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B67" s="2">
         <v>197</v>
@@ -1853,12 +1834,12 @@
         <v>12</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B68" s="2">
         <v>208</v>
@@ -1867,12 +1848,12 @@
         <v>5</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="B69" s="2">
         <v>209</v>
@@ -1881,12 +1862,12 @@
         <v>12</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="B70" s="2">
         <v>210</v>
@@ -1895,12 +1876,12 @@
         <v>12</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B71" s="2">
         <v>211</v>
@@ -1909,12 +1890,12 @@
         <v>5</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B72" s="2">
         <v>213</v>
@@ -1923,12 +1904,12 @@
         <v>12</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B73" s="2">
         <v>214</v>
@@ -1937,12 +1918,12 @@
         <v>12</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="B74" s="2">
         <v>224</v>
@@ -1951,12 +1932,12 @@
         <v>5</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B75" s="2">
         <v>227</v>
@@ -1965,12 +1946,12 @@
         <v>5</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B76" s="2">
         <v>228</v>
@@ -1979,12 +1960,12 @@
         <v>5</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B77" s="2">
         <v>240</v>
@@ -1993,12 +1974,12 @@
         <v>5</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B78" s="2">
         <v>241</v>
@@ -2007,12 +1988,12 @@
         <v>12</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B79" s="2">
         <v>242</v>
@@ -2021,12 +2002,12 @@
         <v>12</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B80" s="2">
         <v>244</v>
@@ -2035,12 +2016,12 @@
         <v>12</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B81" s="2">
         <v>245</v>
@@ -2049,63 +2030,63 @@
         <v>12</v>
       </c>
       <c r="D81" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B82" s="1">
+        <v>246</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A83" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B83" s="1">
+        <v>247</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A82" s="2" t="s">
+    <row r="84" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A84" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B82" s="2">
-        <v>246</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D82" s="2" t="s">
+      <c r="B84" s="1">
+        <v>248</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="83" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A83" s="2" t="s">
+    <row r="85" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A85" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B83" s="2">
-        <v>247</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D83" s="2" t="s">
+      <c r="B85" s="1">
+        <v>249</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>169</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A84" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="B84" s="2">
-        <v>248</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A85" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B85" s="2">
-        <v>249</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>173</v>
       </c>
     </row>
   </sheetData>
